--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/form_field_style.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/form_field_style.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>16.5</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>1.5</v>
+        <v>2.23</v>
       </c>
     </row>
   </sheetData>
